--- a/stories/arbres/ATOM-SAN.HYG.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Rosa sort des toilettes. Papa l'attend dans le couloir. Papa dit : après les toilettes, on lave. Rosa ouvre l'eau. Elle prend le savon. Ça sent le citron. Elle frotte. Elle rince. Elle essuie. Plus tard, c'est l'heure du goûter. Avant de manger, Rosa retourne au lavabo. Elle ouvre l'eau. Elle prend le savon. Elle frotte, elle rince, elle essuie. Papa dit : savon et eau. Rosa va à table. Les mains sont propres.</t>
+          <t>Rosa sort des toilettes. Papa l'attend dans le couloir. Après les toilettes, on lave. Rosa ouvre l'eau. Elle prend le savon. Ça sent le citron. Elle frotte. Elle rince. Elle essuie. Plus tard, c'est l'heure du goûter. Avant de manger, Rosa retourne au lavabo. Elle ouvre l'eau. Elle prend le savon. Elle frotte, elle rince, elle essuie. Savon et eau. Rosa va à table. Les mains sont propres.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Rosa sort des toilettes. Papa l'attend dans le couloir.
+papa|Après les toilettes, on lave.
+narrateur|Rosa ouvre l'eau. Elle prend le savon. Ça sent le citron. Elle frotte. Elle rince. Elle essuie. Plus tard, c'est l'heure du goûter. Avant de manger, Rosa retourne au lavabo. Elle ouvre l'eau. Elle prend le savon. Elle frotte, elle rince, elle essuie.
+papa|Savon et eau.
+narrateur|Rosa va à table. Les mains sont propres.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Rosa se lave les mains. Avec quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Après les toilettes, Rosa a lavé. Avant de manger, Rosa a lavé.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Rosa croque une pomme. Papa s'assoit près d'elle.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Rosa va à table. Les mains sont propres.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Rosa se lave les mains. Avec quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Après les toilettes, Rosa a lavé. Avant de manger, Rosa a lavé.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Rosa croque une pomme. Papa s'assoit près d'elle.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rosa lave ses mains</t>
+          <t>Le savon citron de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La pluie glisse sur la vitre. Mila se lave au savon citron après les toilettes, puis encore avant le goûter. Elle croque une pomme près de papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Rosa sort des toilettes. Papa l'attend dans le couloir. Après les toilettes, on lave. Rosa ouvre l'eau. Elle prend le savon. Ça sent le citron. Elle frotte. Elle rince. Elle essuie. Plus tard, c'est l'heure du goûter. Avant de manger, Rosa retourne au lavabo. Elle ouvre l'eau. Elle prend le savon. Elle frotte, elle rince, elle essuie. Savon et eau. Rosa va à table. Les mains sont propres.</t>
+          <t>Une goutte glisse sur la vitre. Elle laisse un trait brillant. La pluie tapote le toit. Le couloir sent le bois mouillé. Les carreaux sont froids sous les chaussettes. Une serviette jaune pend près du lavabo. L'horloge fait tic, tic, tic. Dehors, une gouttière chante. Mila, je suis dans le couloir. J'arrive, papa. Tu as vu la goutte sur la vitre ? Oui. Elle glisse. En ce moment, Mila sort des toilettes. La porte se ferme tout doucement. Après les toilettes, on lave. Savon et eau. Le savon sent le citron. Oui. Il est jaune, comme la serviette. Mila ouvre l'eau. L'eau est tiède sur ses doigts. Elle prend le savon citron. Elle frotte le dessus des mains. Elle frotte entre les doigts. Elle rince. Les bulles partent. Elle essuie sur la serviette jaune. Bravo. Tes mains sont propres. Tu as fait du bon travail. Elles sentent le citron. Oui. C'est le savon. Mila regarde encore la vitre. Une autre goutte descend. Plus tard, la pluie est plus douce. Ça sent la compote dans la cuisine. C'est l'heure du goûter. Avant de manger, on lave. Je retourne au lavabo. Mila ouvre l'eau. Elle prend le savon. Ça sent encore le citron. Elle frotte, elle rince, elle essuie. Savon et eau. Tu as fini de laver tes mains ? Oui, papa. Bravo. On va à table. Mila va à table. Les mains sont propres. La pomme attend dans l'assiette. L'assiette est blanche, un peu froide.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Rosa sort des toilettes. Papa l'attend dans le couloir.
+          <t>narrateur|Une goutte glisse sur la vitre.
+narrateur|Elle laisse un trait brillant.
+narrateur|La pluie tapote le toit.
+narrateur|Le couloir sent le bois mouillé.
+narrateur|Les carreaux sont froids sous les chaussettes.
+narrateur|Une serviette jaune pend près du lavabo.
+narrateur|L'horloge fait tic, tic, tic.
+narrateur|Dehors, une gouttière chante.
+papa|Mila, je suis dans le couloir.
+enfant-f|J'arrive, papa.
+papa|Tu as vu la goutte sur la vitre ?
+enfant-f|Oui. Elle glisse.
+narrateur|En ce moment, Mila sort des toilettes.
+narrateur|La porte se ferme tout doucement.
 papa|Après les toilettes, on lave.
-narrateur|Rosa ouvre l'eau. Elle prend le savon. Ça sent le citron. Elle frotte. Elle rince. Elle essuie. Plus tard, c'est l'heure du goûter. Avant de manger, Rosa retourne au lavabo. Elle ouvre l'eau. Elle prend le savon. Elle frotte, elle rince, elle essuie.
 papa|Savon et eau.
-narrateur|Rosa va à table. Les mains sont propres.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-f|Le savon sent le citron.
+papa|Oui. Il est jaune, comme la serviette.
+narrateur|Mila ouvre l'eau.
+narrateur|L'eau est tiède sur ses doigts.
+narrateur|Elle prend le savon citron.
+narrateur|Elle frotte le dessus des mains.
+narrateur|Elle frotte entre les doigts.
+narrateur|Elle rince.
+narrateur|Les bulles partent.
+narrateur|Elle essuie sur la serviette jaune.
+papa|Bravo. Tes mains sont propres.
+papa|Tu as fait du bon travail.
+enfant-f|Elles sentent le citron.
+papa|Oui. C'est le savon.
+narrateur|Mila regarde encore la vitre.
+narrateur|Une autre goutte descend.
+narrateur|Plus tard, la pluie est plus douce.
+narrateur|Ça sent la compote dans la cuisine.
+papa|C'est l'heure du goûter.
+papa|Avant de manger, on lave.
+enfant-f|Je retourne au lavabo.
+narrateur|Mila ouvre l'eau.
+narrateur|Elle prend le savon.
+narrateur|Ça sent encore le citron.
+narrateur|Elle frotte, elle rince, elle essuie.
+papa|Savon et eau.
+papa|Tu as fini de laver tes mains ?
+enfant-f|Oui, papa.
+papa|Bravo. On va à table.
+narrateur|Mila va à table.
+narrateur|Les mains sont propres.
+narrateur|La pomme attend dans l'assiette.
+narrateur|L'assiette est blanche, un peu froide.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1399,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Rosa se lave les mains. Avec quoi ?</t>
+          <t>Mila se lave les mains. Avec quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,10 +1559,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Rosa se lave les mains. Avec quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Mila se lave les mains.
+narrateur|Avec quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Après les toilettes, Rosa a lavé. Avant de manger, Rosa a lavé.</t>
+          <t>Après les toilettes, Mila a lavé. Avant de manger, Mila a lavé. Savon et eau, deux fois. Tu te souviens du savon citron ? Oui. Savon et eau. Bravo. C'est le bon geste. La goutte a fini sa course. La vitre est un peu embuée. Mila pose sa main propre sur la table. Tes mains sont prêtes pour la pomme.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,10 +1731,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Après les toilettes, Rosa a lavé. Avant de manger, Rosa a lavé.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Après les toilettes, Mila a lavé.
+narrateur|Avant de manger, Mila a lavé.
+narrateur|Savon et eau, deux fois.
+papa|Tu te souviens du savon citron ?
+enfant-f|Oui. Savon et eau.
+papa|Bravo. C'est le bon geste.
+narrateur|La goutte a fini sa course.
+narrateur|La vitre est un peu embuée.
+narrateur|Mila pose sa main propre sur la table.
+papa|Tes mains sont prêtes pour la pomme.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,7 +1767,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Rosa croque une pomme. Papa s'assoit près d'elle.</t>
+          <t>Mila croque une pomme. La pomme fait un petit bruit. Je m'assois près de toi. La pomme est sucrée. Tes mains sentent le citron. Tu as fini ta pomme ? Presque. Bravo, Mila. La pluie tapote encore, tout doux. L'horloge fait tic, tout lentement. La serviette jaune sèche près du lavabo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,10 +1903,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Rosa croque une pomme. Papa s'assoit près d'elle.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Mila croque une pomme.
+narrateur|La pomme fait un petit bruit.
+papa|Je m'assois près de toi.
+enfant-f|La pomme est sucrée.
+papa|Tes mains sentent le citron.
+papa|Tu as fini ta pomme ?
+enfant-f|Presque.
+papa|Bravo, Mila.
+narrateur|La pluie tapote encore, tout doux.
+narrateur|L'horloge fait tic, tout lentement.
+narrateur|La serviette jaune sèche près du lavabo.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,7 +1940,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a lavé après les toilettes. Mila a lavé avant de manger. Bravo. Tes mains sont propres. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,10 +2080,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Mila a lavé après les toilettes.
+narrateur|Mila a lavé avant de manger.
+papa|Bravo. Tes mains sont propres.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2142,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une goutte glisse sur la vitre. Elle laisse un trait brillant. La pluie tapote le toit. Le couloir sent le bois mouillé. Les carreaux sont froids sous les chaussettes. Une serviette jaune pend près du lavabo. L'horloge fait tic, tic, tic. Dehors, une gouttière chante. Mila, je suis dans le couloir. J'arrive, papa. Tu as vu la goutte sur la vitre ? Oui. Elle glisse. En ce moment, Mila sort des toilettes. La porte se ferme tout doucement. Après les toilettes, on lave. Savon et eau. Le savon sent le citron. Oui. Il est jaune, comme la serviette. Mila ouvre l'eau. L'eau est tiède sur ses doigts. Elle prend le savon citron. Elle frotte le dessus des mains. Elle frotte entre les doigts. Elle rince. Les bulles partent. Elle essuie sur la serviette jaune. Bravo. Tes mains sont propres. Tu as fait du bon travail. Elles sentent le citron. Oui. C'est le savon. Mila regarde encore la vitre. Une autre goutte descend. Plus tard, la pluie est plus douce. Ça sent la compote dans la cuisine. C'est l'heure du goûter. Avant de manger, on lave. Je retourne au lavabo. Mila ouvre l'eau. Elle prend le savon. Ça sent encore le citron. Elle frotte, elle rince, elle essuie. Savon et eau. Tu as fini de laver tes mains ? Oui, papa. Bravo. On va à table. Mila va à table. Les mains sont propres. La pomme attend dans l'assiette. L'assiette est blanche, un peu froide.</t>
+          <t>Une goutte glisse sur la vitre. Elle laisse un trait brillant. La pluie tapote le toit. Le couloir sent le bois mouillé. Les carreaux sont froids sous les chaussettes. Une serviette jaune pend près du lavabo. L'horloge fait tic, tic, tic. Dehors, une gouttière chante. Mila, viens. Le lavabo est prêt. J'arrive, papa. Tu as vu la goutte sur la vitre ? Oui. Elle glisse. En ce moment, Mila sort des toilettes. La porte se ferme tout doucement. Après les toilettes, on lave. Savon et eau. Le savon sent le citron. Oui. Il est jaune, comme la serviette. Mila ouvre l'eau. L'eau est tiède sur ses doigts. Elle prend le savon citron. Elle frotte le dessus des mains. Elle frotte entre les doigts. Elle rince. Les bulles partent. Elle essuie sur la serviette jaune. Bravo. Tes mains sont propres. Elles sentent le citron. Oui. C'est le savon. Mila regarde encore la vitre. Une autre goutte descend. Tu as les mains propres, maintenant ? Oui, papa. Bravo. Plus tard, la pluie est plus douce. Ça sent la compote dans la cuisine. C'est l'heure du goûter. Avant de manger, on lave. Je retourne au lavabo. Mila ouvre l'eau. Elle prend le savon. Ça sent encore le citron. Elle frotte, elle rince, elle essuie. Savon et eau. Tu as fini de laver tes mains ? Oui, papa. Bravo. On va à table. Mila va à table. Les mains sont propres. La pomme attend dans l'assiette. L'assiette est blanche, un peu froide.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Rosa sort des toilettes. Papa l'attend dans le couloir. Papa dit : après les toilettes, on lave. Rosa ouvre l'eau. Elle prend le &lt;emphasis level="moderate"&gt;savon&lt;/emphasis&gt;. Ça sent le citron. Elle frotte. Elle rince. Elle essuie. Plus tard, c'est l'heure du goûter. Avant de manger, Rosa retourne au lavabo. Elle ouvre l'eau. Elle prend le savon. Elle frotte, elle rince, elle essuie. Papa dit : savon et eau. Rosa va à table. Les mains sont propres.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une goutte glisse sur la vitre. Elle laisse un trait brillant. La pluie tapote le toit. Le couloir sent le bois mouillé. Les carreaux sont froids sous les chaussettes. Une serviette jaune pend près du lavabo. L'horloge fait tic, tic, tic. Dehors, une gouttière chante. Mila, viens. Le lavabo est prêt. J'arrive, papa. Tu as vu la goutte sur la vitre ? Oui. Elle glisse. En ce moment, Mila sort des toilettes. La porte se ferme tout doucement. Après les toilettes, on lave. Savon et eau. Le savon sent le citron. Oui. Il est jaune, comme la serviette. Mila ouvre l'eau. L'eau est tiède sur ses doigts. Elle prend le savon citron. Elle frotte le dessus des mains. Elle frotte entre les doigts. Elle rince. Les bulles partent. Elle essuie sur la serviette jaune. Bravo. Tes mains sont propres. Elles sentent le citron. Oui. C'est le savon. Mila regarde encore la vitre. Une autre goutte descend. Tu as les mains propres, maintenant ? Oui, papa. Bravo. Plus tard, la pluie est plus douce. Ça sent la compote dans la cuisine. C'est l'heure du goûter. Avant de manger, on lave. Je retourne au lavabo. Mila ouvre l'eau. Elle prend le savon. Ça sent encore le citron. Elle frotte, elle rince, elle essuie. Savon et eau. Tu as fini de laver tes mains ? Oui, papa. Bravo. On va à table. Mila va à table. Les mains sont propres. La pomme attend dans l'assiette. L'assiette est blanche, un peu froide.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
 narrateur|Une serviette jaune pend près du lavabo.
 narrateur|L'horloge fait tic, tic, tic.
 narrateur|Dehors, une gouttière chante.
-papa|Mila, je suis dans le couloir.
+papa|Mila, viens. Le lavabo est prêt.
 enfant-f|J'arrive, papa.
 papa|Tu as vu la goutte sur la vitre ?
 enfant-f|Oui. Elle glisse.
@@ -1351,11 +1351,13 @@
 narrateur|Les bulles partent.
 narrateur|Elle essuie sur la serviette jaune.
 papa|Bravo. Tes mains sont propres.
-papa|Tu as fait du bon travail.
 enfant-f|Elles sentent le citron.
 papa|Oui. C'est le savon.
 narrateur|Mila regarde encore la vitre.
 narrateur|Une autre goutte descend.
+papa|Tu as les mains propres, maintenant ?
+enfant-f|Oui, papa.
+papa|Bravo.
 narrateur|Plus tard, la pluie est plus douce.
 narrateur|Ça sent la compote dans la cuisine.
 papa|C'est l'heure du goûter.
@@ -1404,7 +1406,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Rosa se lave les &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s. Avec quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila se lave les mains. Avec quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1592,7 +1594,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Après les toilettes, Rosa a lavé. &lt;emphasis level="moderate"&gt;avant&lt;/emphasis&gt; de manger, Rosa a lavé.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Après les toilettes, Mila a lavé. Avant de manger, Mila a lavé. Savon et eau, deux fois. Tu te souviens du savon citron ? Oui. Savon et eau. Bravo. C'est le bon geste. La goutte a fini sa course. La vitre est un peu embuée. Mila pose sa main propre sur la table. Tes mains sont prêtes pour la pomme.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1772,7 +1774,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Rosa croque une pomme. Papa s'assoit près d'elle.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila croque une pomme. La pomme fait un petit bruit. Je m'assois près de toi. La pomme est sucrée. Tes mains sentent le citron. Tu as fini ta pomme ? Presque. Bravo, Mila. La pluie tapote encore, tout doux. L'horloge fait tic, tout lentement. La serviette jaune sèche près du lavabo.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1940,12 +1942,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mila a lavé après les toilettes. Mila a lavé avant de manger. Bravo. Tes mains sont propres. L'histoire est finie.</t>
+          <t>Mila a lavé après les toilettes. Mila a lavé avant de manger. Bravo. Tes mains sont propres.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a lavé après les toilettes. Mila a lavé avant de manger. Bravo. Tes mains sont propres.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2082,8 +2084,7 @@
         <is>
           <t>narrateur|Mila a lavé après les toilettes.
 narrateur|Mila a lavé avant de manger.
-papa|Bravo. Tes mains sont propres.
-narrateur|L'histoire est finie.</t>
+papa|Bravo. Tes mains sont propres.</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2149,6 +2150,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.001-04.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison</t>
+          <t>maison, jour de pluie</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rosa, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
